--- a/review-results/复盘信息抓取-20260805.xlsx
+++ b/review-results/复盘信息抓取-20260805.xlsx
@@ -5049,10 +5049,10 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="2"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
     <col width="22" customWidth="1" min="8" max="9"/>
@@ -5115,8 +5115,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>18209.923</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>402.693</v>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5140,8 +5159,27 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>18358.049</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>411.818</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5165,8 +5203,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>16065.623</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>368.643</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5190,8 +5247,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>15227.866</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>361.165</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5215,8 +5291,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>15246.811</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>366.21</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5240,8 +5335,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>17259.972</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>409.723</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5265,8 +5379,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>19083.663</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>418.395</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5290,8 +5423,27 @@
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>20263.964</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>401.725</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5315,8 +5467,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>21039.528</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>363.878</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5340,8 +5511,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>21439.185</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>337.748</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5365,8 +5555,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>22670.383</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>335.393</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5390,8 +5599,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>24134.494</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>348.55</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5415,8 +5643,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>26024.605</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>392.518</v>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5440,8 +5687,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>25422.135</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>379.858</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5465,8 +5731,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>24102.061</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>367.618</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5490,8 +5775,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>23965.443</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>388.193</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5515,8 +5819,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>24398.215</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>433.14</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5540,8 +5863,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>24734.404</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>456.003</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5565,8 +5907,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>25747.866</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>479.52</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5590,8 +5951,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>25490.747</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>469.278</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5615,8 +5995,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>25296.183</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>481.317</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5640,8 +6039,27 @@
       </c>
     </row>
     <row r="23">
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>24745.626</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>474.596</v>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5665,8 +6083,27 @@
       </c>
     </row>
     <row r="24">
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>24397.727</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>471.687</v>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -5690,8 +6127,27 @@
       </c>
     </row>
     <row r="25">
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>现货实时交易价格曲线</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>22593.595</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>459.418</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>现货日前交易价格曲线</t>
@@ -17796,7 +18252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>现货日前交易价格曲线</t>
+          <t>现货实时交易价格曲线</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -17809,20 +18265,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>实际系统负荷</t>
+          <t>现货日前交易价格曲线</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新能源实际发电曲线</t>
+          <t>实际系统负荷</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17835,7 +18291,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日前非市场化机组总出力</t>
+          <t>新能源实际发电曲线</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -17848,7 +18304,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>省间联络线输电情况</t>
+          <t>日前非市场化机组总出力</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -17861,24 +18317,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>省间联络线输电情况</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>960</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>768</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -17887,30 +18343,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>日前储能充电计划及电价</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>日前储能充电计划及电价</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/review-results/复盘信息抓取-20260805.xlsx
+++ b/review-results/复盘信息抓取-20260805.xlsx
@@ -1043,20 +1043,20 @@
   <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -5049,17 +5049,15 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6184,33 +6182,31 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="26"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="24"/>
+    <col width="5" customWidth="1" min="25" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15576,12 +15572,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18227,9 +18222,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
